--- a/private/planilla-mi-sueldo-2026.xlsx
+++ b/private/planilla-mi-sueldo-2026.xlsx
@@ -410,7 +410,7 @@
     <t>IPC Nacional del INDEC — nivel general (base diciembre 2016 = 100)</t>
   </si>
   <si>
-    <t>Serie oficial descargada el 2026-09-28 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
+    <t>Serie oficial descargada el 2026-10-07 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
   </si>
   <si>
     <t>Período</t>
@@ -1055,43 +1055,43 @@
     <t>Link</t>
   </si>
   <si>
-    <t>Ley 24.241, art. 11 — aporte personal jubilatorio 11% (SIPA)</t>
+    <t>Ley 24.241, art. 11: aporte personal jubilatorio 11% (SIPA)</t>
   </si>
   <si>
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/0-4999/639/texact.htm</t>
   </si>
   <si>
-    <t>Ley 19.032 — INSSJP / PAMI 3%</t>
+    <t>Ley 19.032: INSSJP / PAMI 3%</t>
   </si>
   <si>
     <t>https://www.argentina.gob.ar/normativa/nacional/ley-19032-21581</t>
   </si>
   <si>
-    <t>Ley 23.660 — aporte del trabajador a la obra social 3%</t>
+    <t>Ley 23.660: aporte del trabajador a la obra social 3%</t>
   </si>
   <si>
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/0-4999/62/texact.htm</t>
   </si>
   <si>
-    <t>Resolución ANSES 257/2026 — bases imponibles desde el devengado septiembre 2026</t>
+    <t>Resolución ANSES 257/2026: bases imponibles desde el devengado septiembre 2026</t>
   </si>
   <si>
     <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346683/20260901</t>
   </si>
   <si>
-    <t>INDEC — IPC Nacional, nivel general (API oficial de series de tiempo)</t>
+    <t>INDEC: IPC Nacional, nivel general (API oficial de series de tiempo)</t>
   </si>
   <si>
     <t>https://datos.gob.ar/series/api/series/?ids=148.3_INIVELNAL_DICI_M_26&amp;format=json</t>
   </si>
   <si>
-    <t>INDEC — Índice de precios al consumidor (informes técnicos mensuales)</t>
+    <t>INDEC: Índice de precios al consumidor (informes técnicos mensuales)</t>
   </si>
   <si>
     <t>https://www.indec.gob.ar/indec/web/Nivel4-Tema-3-5-31</t>
   </si>
   <si>
-    <t>Ley 23.041 — Sueldo Anual Complementario</t>
+    <t>Ley 23.041: Sueldo Anual Complementario</t>
   </si>
   <si>
     <t>https://www.argentina.gob.ar/normativa/nacional/ley-23041-1983-28165</t>
@@ -1103,19 +1103,19 @@
     <t>https://servicios.infoleg.gob.ar/infolegInternet/anexos/25000-29999/25552/texact.htm</t>
   </si>
   <si>
-    <t>ARCA — Deducciones personales art. 30 LIG (julio a diciembre 2026)</t>
+    <t>ARCA: Deducciones personales art. 30 LIG (julio a diciembre 2026)</t>
   </si>
   <si>
     <t>https://www.afip.gob.ar/gananciasYBienes/ganancias/personas-humanas-sucesiones-indivisas/deducciones/documentos/Deducciones-personales-art-30-jul-dic-2026.pdf</t>
   </si>
   <si>
-    <t>Decreto 407/2026 — reglamenta la Ley 27.802 de Modernización Laboral (art. 140 LCT)</t>
+    <t>Decreto 407/2026: reglamenta la Ley 27.802 de Modernización Laboral (art. 140 LCT)</t>
   </si>
   <si>
     <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/342620/20260601</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-09-28; tope de aportes de octubre de 2026; deducciones de Ganancias del 2do semestre 2026 (julio a diciembre) (ARCA, consultadas el 29 de julio de 2026). Cuando cambia uno de estos datos regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-10-07; tope de aportes de octubre de 2026; deducciones de Ganancias del 2do semestre 2026 (julio a diciembre) (ARCA, consultadas el 29 de julio de 2026). Cuando cambia uno de estos datos regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>

--- a/private/planilla-mi-sueldo-2026.xlsx
+++ b/private/planilla-mi-sueldo-2026.xlsx
@@ -410,7 +410,7 @@
     <t>IPC Nacional del INDEC — nivel general (base diciembre 2016 = 100)</t>
   </si>
   <si>
-    <t>Serie oficial descargada el 2026-10-07 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
+    <t>Serie oficial descargada el 2026-10-15 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
   </si>
   <si>
     <t>Período</t>
@@ -1115,7 +1115,7 @@
     <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/342620/20260601</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-10-07; tope de aportes de octubre de 2026; deducciones de Ganancias del 2do semestre 2026 (julio a diciembre) (ARCA, consultadas el 29 de julio de 2026). Cuando cambia uno de estos datos regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-10-15; tope de aportes de octubre de 2026; deducciones de Ganancias del 2do semestre 2026 (julio a diciembre) (ARCA, consultadas el 29 de julio de 2026). Cuando cambia uno de estos datos regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>

--- a/private/planilla-mi-sueldo-2026.xlsx
+++ b/private/planilla-mi-sueldo-2026.xlsx
@@ -410,7 +410,7 @@
     <t>IPC Nacional del INDEC — nivel general (base diciembre 2016 = 100)</t>
   </si>
   <si>
-    <t>Serie oficial descargada el 2026-10-15 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
+    <t>Serie oficial descargada el 2026-10-23 de la API de series de tiempo del Estado (datos.gob.ar). Último dato: agosto de 2026. Si ya salió un mes que acá no está, cargá su % en la columna amarilla.</t>
   </si>
   <si>
     <t>Período</t>
@@ -1115,7 +1115,7 @@
     <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/342620/20260601</t>
   </si>
   <si>
-    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-10-15; tope de aportes de octubre de 2026; deducciones de Ganancias del 2do semestre 2026 (julio a diciembre) (ARCA, consultadas el 29 de julio de 2026). Cuando cambia uno de estos datos regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
+    <t>Planilla de calcular.ar. Serie del IPC descargada el 2026-10-23; tope de aportes de octubre de 2026; deducciones de Ganancias del 2do semestre 2026 (julio a diciembre) (ARCA, consultadas el 29 de julio de 2026). Cuando cambia uno de estos datos regeneramos el archivo: el mismo enlace de descarga te baja la versión al día, sin costo.</t>
   </si>
 </sst>
 </file>
